--- a/kix-model/KIX_Venue_Model.xlsx
+++ b/kix-model/KIX_Venue_Model.xlsx
@@ -14,6 +14,8 @@
     <sheet name="Capex" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="P&amp;L" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Returns &amp; Scenarios" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Capital Stack" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Debt &amp; DSCR" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -139,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -206,6 +208,8 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4038,11 +4042,11 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>P&amp;L!D7</f>
+        <f>'P&amp;L'!D7</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>P&amp;L!D30</f>
+        <f>'P&amp;L'!D30</f>
         <v/>
       </c>
     </row>
@@ -4053,11 +4057,11 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>P&amp;L!D23</f>
+        <f>'P&amp;L'!D23</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>P&amp;L!D46</f>
+        <f>'P&amp;L'!D46</f>
         <v/>
       </c>
     </row>
@@ -4068,11 +4072,11 @@
         </is>
       </c>
       <c r="B9" s="22">
-        <f>P&amp;L!D24</f>
+        <f>'P&amp;L'!D24</f>
         <v/>
       </c>
       <c r="C9" s="22">
-        <f>P&amp;L!D47</f>
+        <f>'P&amp;L'!D47</f>
         <v/>
       </c>
     </row>
@@ -4083,11 +4087,11 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>P&amp;L!F23</f>
+        <f>'P&amp;L'!F23</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>P&amp;L!F46</f>
+        <f>'P&amp;L'!F46</f>
         <v/>
       </c>
     </row>
@@ -4098,11 +4102,11 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>P&amp;L!F25</f>
+        <f>'P&amp;L'!F25</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>P&amp;L!F48</f>
+        <f>'P&amp;L'!F48</f>
         <v/>
       </c>
     </row>
@@ -4596,6 +4600,1338 @@
       <c r="A49" s="12" t="inlineStr">
         <is>
           <t>and spend a day at ESA's own FTY Lab in Poole counting throughput per station per hour.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CAPITAL STACK — SBA &amp; CREATIVE FINANCING</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Total project cost including real estate, and how it gets funded. All rates and structures are planning assumptions — confirm every one with your lender and CDC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>18,000 SF</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>35,000 SF</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>REAL ESTATE (BUY CASE)</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Building purchase price per SF ($)</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="n">
+        <v>150</v>
+      </c>
+      <c r="C6" s="29" t="n">
+        <v>150</v>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Sarasota / Bradenton warehouse-flex. Verify against live comps</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Building size (SF)</t>
+        </is>
+      </c>
+      <c r="B7" s="32">
+        <f>Assumptions!$B$7</f>
+        <v/>
+      </c>
+      <c r="C7" s="32">
+        <f>Assumptions!$C$7</f>
+        <v/>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>SBA requires you to occupy at least 51%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Building purchase price</t>
+        </is>
+      </c>
+      <c r="B8" s="16">
+        <f>B7*B6</f>
+        <v/>
+      </c>
+      <c r="C8" s="16">
+        <f>C7*C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Acquisition costs (% of price)</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Survey, environmental, legal, title, appraisal</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Acquisition costs</t>
+        </is>
+      </c>
+      <c r="B10" s="16">
+        <f>B8*B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="16">
+        <f>C8*C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>Real estate subtotal</t>
+        </is>
+      </c>
+      <c r="B11" s="39">
+        <f>B8+B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="39">
+        <f>C8+C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>TOTAL PROJECT COST</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Venue project cost (from Capex)</t>
+        </is>
+      </c>
+      <c r="B14" s="44">
+        <f>Capex!$B$13</f>
+        <v/>
+      </c>
+      <c r="C14" s="44">
+        <f>Capex!$C$13</f>
+        <v/>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Fit-out, ESA equipment, FF&amp;E, tech, pre-opening</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Working capital &amp; debt service reserve</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="n">
+        <v>350000</v>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>550000</v>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>CRITICAL. Year 1 does not cover debt service — see the DSCR sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL PROJECT COST — BUY</t>
+        </is>
+      </c>
+      <c r="B16" s="35">
+        <f>B11+B14+B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="35">
+        <f>C11+C14+C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Landlord TI allowance per SF ($) — lease case</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Negotiable. A startup covenant gets less than an established one</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Landlord TI allowance</t>
+        </is>
+      </c>
+      <c r="B18" s="16">
+        <f>Assumptions!$B$7*B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="16">
+        <f>Assumptions!$C$7*C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL PROJECT COST — LEASE</t>
+        </is>
+      </c>
+      <c r="B19" s="35">
+        <f>B14-B18+B15</f>
+        <v/>
+      </c>
+      <c r="C19" s="35">
+        <f>C14-C18+C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>SBA 504 TRANCHE (BUY CASE)</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>504 funds real estate and long-life equipment. Fit-out is real-property improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>504-eligible project cost</t>
+        </is>
+      </c>
+      <c r="B23" s="16">
+        <f>B11+Assumptions!$B$7*Assumptions!$B$44+Capex!$B$7</f>
+        <v/>
+      </c>
+      <c r="C23" s="16">
+        <f>C11+Assumptions!$C$7*Assumptions!$C$44+Capex!$C$7</f>
+        <v/>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Real estate + fit-out + ESA equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Borrower injection (%)</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C24" s="28" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Standard 504 is 10%. Add 5% for a startup and 5% for a special-purpose property. An entertainment venue is almost certainly both — plan for 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Bank first mortgage (%)</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Conventional first lien</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>CDC / SBA debenture (%)</t>
+        </is>
+      </c>
+      <c r="B26" s="22">
+        <f>1-B24-B25</f>
+        <v/>
+      </c>
+      <c r="C26" s="22">
+        <f>1-C24-C25</f>
+        <v/>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Second lien, below-market fixed rate, fully amortising</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Bank first mortgage</t>
+        </is>
+      </c>
+      <c r="B27" s="16">
+        <f>B23*B25</f>
+        <v/>
+      </c>
+      <c r="C27" s="16">
+        <f>C23*C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>CDC / SBA 504 debenture</t>
+        </is>
+      </c>
+      <c r="B28" s="16">
+        <f>B23*B26</f>
+        <v/>
+      </c>
+      <c r="C28" s="16">
+        <f>C23*C26</f>
+        <v/>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Debenture caps apply — confirm the current limit with your CDC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Injection against 504</t>
+        </is>
+      </c>
+      <c r="B29" s="16">
+        <f>B23*B24</f>
+        <v/>
+      </c>
+      <c r="C29" s="16">
+        <f>C23*C24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>SBA 7(a) TRANCHE</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Costs not covered by 504</t>
+        </is>
+      </c>
+      <c r="B32" s="16">
+        <f>B16-B23</f>
+        <v/>
+      </c>
+      <c r="C32" s="16">
+        <f>C16-C23</f>
+        <v/>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>FF&amp;E, technology, pre-opening, contingency, working capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>7(a) advance rate (%)</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Lender-dependent. Startups typically inject 10-20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>SBA 7(a) loan</t>
+        </is>
+      </c>
+      <c r="B34" s="16">
+        <f>B32*B33</f>
+        <v/>
+      </c>
+      <c r="C34" s="16">
+        <f>C32*C33</f>
+        <v/>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>7(a) programme maximum applies — confirm with your lender</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Injection against 7(a)</t>
+        </is>
+      </c>
+      <c r="B35" s="16">
+        <f>B32-B34</f>
+        <v/>
+      </c>
+      <c r="C35" s="16">
+        <f>C32-C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>FUNDING SUMMARY — BUY CASE</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>Total debt</t>
+        </is>
+      </c>
+      <c r="B38" s="41">
+        <f>B27+B28+B34</f>
+        <v/>
+      </c>
+      <c r="C38" s="41">
+        <f>C27+C28+C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>Total equity required</t>
+        </is>
+      </c>
+      <c r="B39" s="52">
+        <f>B29+B35</f>
+        <v/>
+      </c>
+      <c r="C39" s="52">
+        <f>C29+C35</f>
+        <v/>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>The cash you actually have to find</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Check: debt + equity = project cost</t>
+        </is>
+      </c>
+      <c r="B40" s="16">
+        <f>B38+B39-B16</f>
+        <v/>
+      </c>
+      <c r="C40" s="16">
+        <f>C38+C39-C16</f>
+        <v/>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>Must be zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Debt as % of total cost</t>
+        </is>
+      </c>
+      <c r="B41" s="22">
+        <f>B38/B16</f>
+        <v/>
+      </c>
+      <c r="C41" s="22">
+        <f>C38/C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>CREATIVE FINANCING — REDUCING THE EQUITY CHEQUE</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Each of these lowers the cash you inject. Model them, then negotiate them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Founding memberships presold (cash pre-opening)</t>
+        </is>
+      </c>
+      <c r="B45" s="29" t="n">
+        <v>150000</v>
+      </c>
+      <c r="C45" s="29" t="n">
+        <v>200000</v>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Non-dilutive, and the only line here that also proves demand. Do this first</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>ESA equipment on lease or vendor terms</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>Ask ESA to lease rather than sell. Moves capex to opex</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Seller financing on the building</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Second behind the bank. Requires lender standby consent</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Party &amp; corporate booking deposits</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>Small, but it is float you would otherwise borrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>Total creative financing</t>
+        </is>
+      </c>
+      <c r="B49" s="39">
+        <f>SUM(B45:B48)</f>
+        <v/>
+      </c>
+      <c r="C49" s="39">
+        <f>SUM(C45:C48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>NET EQUITY REQUIRED</t>
+        </is>
+      </c>
+      <c r="B50" s="35">
+        <f>B39-B49</f>
+        <v/>
+      </c>
+      <c r="C50" s="35">
+        <f>C39-C49</f>
+        <v/>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>Lenders may not count all of these toward the required injection — ask first</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DEBT SERVICE &amp; DSCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>DSCR is the number the lender underwrites. Everything else is a conversation; this is the test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>RATES &amp; TERMS</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Years</t>
+        </is>
+      </c>
+      <c r="E5" s="40" t="inlineStr">
+        <is>
+          <t>Annual payment</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr"/>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Bank first mortgage (504)</t>
+        </is>
+      </c>
+      <c r="B6" s="44">
+        <f>'Capital Stack'!$B$27</f>
+        <v/>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="E6" s="16">
+        <f>IF(B6=0,0,-PMT(C6/12,D6*12,B6)*12)</f>
+        <v/>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Conventional first lien, 25-year amortisation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>CDC / SBA 504 debenture</t>
+        </is>
+      </c>
+      <c r="B7" s="44">
+        <f>'Capital Stack'!$B$28</f>
+        <v/>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" s="16">
+        <f>IF(B7=0,0,-PMT(C7/12,D7*12,B7)*12)</f>
+        <v/>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Below-market fixed. This is the cheap money in the stack</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>SBA 7(a)</t>
+        </is>
+      </c>
+      <c r="B8" s="44">
+        <f>'Capital Stack'!$B$34</f>
+        <v/>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="16">
+        <f>IF(B8=0,0,-PMT(C8/12,D8*12,B8)*12)</f>
+        <v/>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Variable, typically prime plus a spread. Model it high</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Total annual debt service</t>
+        </is>
+      </c>
+      <c r="B9" s="39">
+        <f>SUM(B6:B8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="35">
+        <f>SUM(E6:E8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>CASH AVAILABLE FOR DEBT SERVICE — 18,000 SF, BUY CASE</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>Year 1</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>Year 2</t>
+        </is>
+      </c>
+      <c r="D12" s="40" t="inlineStr">
+        <is>
+          <t>Year 3</t>
+        </is>
+      </c>
+      <c r="E12" s="40" t="inlineStr">
+        <is>
+          <t>Year 4</t>
+        </is>
+      </c>
+      <c r="F12" s="40" t="inlineStr">
+        <is>
+          <t>Year 5</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Venue EBITDA (leased basis)</t>
+        </is>
+      </c>
+      <c r="B13" s="44">
+        <f>'P&amp;L'!B23</f>
+        <v/>
+      </c>
+      <c r="C13" s="44">
+        <f>'P&amp;L'!C23</f>
+        <v/>
+      </c>
+      <c r="D13" s="44">
+        <f>'P&amp;L'!D23</f>
+        <v/>
+      </c>
+      <c r="E13" s="44">
+        <f>'P&amp;L'!E23</f>
+        <v/>
+      </c>
+      <c r="F13" s="44">
+        <f>'P&amp;L'!F23</f>
+        <v/>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>From the P&amp;L, which assumes you pay rent</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Add back: rent (you own the building)</t>
+        </is>
+      </c>
+      <c r="B14" s="16">
+        <f>Assumptions!$B$7*Assumptions!$B$53</f>
+        <v/>
+      </c>
+      <c r="C14" s="16">
+        <f>Assumptions!$B$7*Assumptions!$B$53</f>
+        <v/>
+      </c>
+      <c r="D14" s="16">
+        <f>Assumptions!$B$7*Assumptions!$B$53</f>
+        <v/>
+      </c>
+      <c r="E14" s="16">
+        <f>Assumptions!$B$7*Assumptions!$B$53</f>
+        <v/>
+      </c>
+      <c r="F14" s="16">
+        <f>Assumptions!$B$7*Assumptions!$B$53</f>
+        <v/>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Owning replaces rent with debt service</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Less: property tax &amp; owner costs</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>% of building value — Florida commercial. Edit this cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Property tax &amp; owner costs</t>
+        </is>
+      </c>
+      <c r="B16" s="16">
+        <f>'Capital Stack'!$B$8*$B$15</f>
+        <v/>
+      </c>
+      <c r="C16" s="16">
+        <f>'Capital Stack'!$B$8*$B$15</f>
+        <v/>
+      </c>
+      <c r="D16" s="16">
+        <f>'Capital Stack'!$B$8*$B$15</f>
+        <v/>
+      </c>
+      <c r="E16" s="16">
+        <f>'Capital Stack'!$B$8*$B$15</f>
+        <v/>
+      </c>
+      <c r="F16" s="16">
+        <f>'Capital Stack'!$B$8*$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Cash available for debt service</t>
+        </is>
+      </c>
+      <c r="B17" s="35">
+        <f>B13+B14-B16</f>
+        <v/>
+      </c>
+      <c r="C17" s="35">
+        <f>C13+C14-C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="35">
+        <f>D13+D14-D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="35">
+        <f>E13+E14-E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="35">
+        <f>F13+F14-F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Annual debt service</t>
+        </is>
+      </c>
+      <c r="B18" s="16">
+        <f>$E$9</f>
+        <v/>
+      </c>
+      <c r="C18" s="16">
+        <f>$E$9</f>
+        <v/>
+      </c>
+      <c r="D18" s="16">
+        <f>$E$9</f>
+        <v/>
+      </c>
+      <c r="E18" s="16">
+        <f>$E$9</f>
+        <v/>
+      </c>
+      <c r="F18" s="16">
+        <f>$E$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>DSCR</t>
+        </is>
+      </c>
+      <c r="B19" s="53">
+        <f>IF(B18=0,0,B17/B18)</f>
+        <v/>
+      </c>
+      <c r="C19" s="53">
+        <f>IF(C18=0,0,C17/C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="53">
+        <f>IF(D18=0,0,D17/D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="53">
+        <f>IF(E18=0,0,E17/E18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="53">
+        <f>IF(F18=0,0,F17/F18)</f>
+        <v/>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Lenders typically want 1.25x or better</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Covenant minimum</t>
+        </is>
+      </c>
+      <c r="B20" s="46" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>Pass / fail</t>
+        </is>
+      </c>
+      <c r="B21" s="40">
+        <f>IF(B19&gt;=$B$20,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="C21" s="40">
+        <f>IF(C19&gt;=$B$20,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="D21" s="40">
+        <f>IF(D19&gt;=$B$20,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="E21" s="40">
+        <f>IF(E19&gt;=$B$20,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F21" s="40">
+        <f>IF(F19&gt;=$B$20,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>A Year 1 fail is normal for a startup venue — it is why the reserve exists</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Cash flow after debt service</t>
+        </is>
+      </c>
+      <c r="B22" s="16">
+        <f>B17-B18</f>
+        <v/>
+      </c>
+      <c r="C22" s="16">
+        <f>C17-C18</f>
+        <v/>
+      </c>
+      <c r="D22" s="16">
+        <f>D17-D18</f>
+        <v/>
+      </c>
+      <c r="E22" s="16">
+        <f>E17-E18</f>
+        <v/>
+      </c>
+      <c r="F22" s="16">
+        <f>F17-F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>Cumulative cash flow after debt service</t>
+        </is>
+      </c>
+      <c r="B23" s="41">
+        <f>B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="41">
+        <f>B23+C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="41">
+        <f>C23+D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="41">
+        <f>D23+E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="41">
+        <f>E23+F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>The most negative figure here is the minimum reserve you must fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>RETURN ON EQUITY</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>Net equity injected</t>
+        </is>
+      </c>
+      <c r="B26" s="44">
+        <f>'Capital Stack'!$B$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Year 3 cash flow after debt service</t>
+        </is>
+      </c>
+      <c r="B27" s="16">
+        <f>D22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Year 3 cash-on-cash on equity</t>
+        </is>
+      </c>
+      <c r="B28" s="43">
+        <f>IF(B26&lt;=0,0,B27/B26)</f>
+        <v/>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Before principal paydown and any property appreciation</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>Year 5 cash-on-cash on equity</t>
+        </is>
+      </c>
+      <c r="B29" s="43">
+        <f>IF(B26&lt;=0,0,F22/B26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>THINGS TO CONFIRM BEFORE YOU BANK ON THIS</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>SBA eligibility depends on the ownership being US citizens or lawful permanent residents. If the</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>ownership is non-US, the SBA route may not be available at all. Establish this before anything else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Every owner of 20% or more gives an unlimited personal guarantee. Understand what you are signing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>504 debenture and 7(a) programme maximums, and whether the two can be combined at this size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Whether presold memberships and deposits count toward the required equity injection. Often they do not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Rates here are planning placeholders. Get a real term sheet before this model informs a decision.</t>
         </is>
       </c>
     </row>
